--- a/docs/BugHunters_Story_Task_Tracker.xlsx
+++ b/docs/BugHunters_Story_Task_Tracker.xlsx
@@ -1,60 +1,404 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>Microsoft Excel</Application>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <sheets>
+    <sheet name="Team Story Assignments" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Commit and PR Tracker" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+  </sheets>
+  <definedNames/>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <dc:creator>GitHub Copilot</dc:creator>
-  <cp:lastModifiedBy>GitHub Copilot</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-08-05T06:30:21Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-08-05T06:30:21Z</dcterms:modified>
-  <dc:title>BugHunters Story and Task Tracker</dc:title>
-</cp:coreProperties>
-</file>
-
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <name val="Calibri"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="1">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
   </fills>
   <borders count="1">
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheets>
-    <sheet name="Team Story Assignments" sheetId="1" r:id="rId1"/>
-    <sheet name="Commit and PR Tracker" sheetId="2" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" r:id="rId3"/>
-  </sheets>
-</workbook>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -64,50 +408,30 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Teammate</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Teammate</t>
+          <t>Assigned Date</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Assigned Date</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>Due Date</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Health</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
@@ -121,50 +445,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Core Backend</t>
+          <t>Payment domain models</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Payment domain models</t>
+          <t>Implement Payment and PaymentHistory entities</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Implement Payment and PaymentHistory entities</t>
+          <t>Chakrika Sai</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
         <is>
           <t>PR #1, PR #2</t>
         </is>
@@ -178,50 +482,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>Account schema and JPA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Account schema and JPA</t>
+          <t>Create account table schema and repository setup</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Create account table schema and repository setup</t>
+          <t>KVS Ganesh</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KVS Ganesh</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
         <is>
           <t>Commits df81852, 1c57902</t>
         </is>
@@ -235,50 +519,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>API Layer</t>
+          <t>Payment endpoints</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Payment endpoints</t>
+          <t>Build create/get payment APIs</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Build create/get payment APIs</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
         <is>
           <t>Commit 73685f9, PR #5</t>
         </is>
@@ -292,50 +556,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Unit testing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Unit testing</t>
+          <t>Add backend unit test coverage</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Add backend unit test coverage</t>
+          <t>Hamsa Suresh</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hamsa Suresh</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
         <is>
           <t>Commit 0bbdc5e, PR #9</t>
         </is>
@@ -349,50 +593,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>Exception handling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Exception handling</t>
+          <t>Implement global exception handling and mapping</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Implement global exception handling and mapping</t>
+          <t>Chakrika Sai</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
         <is>
           <t>Commit 8820d8a, PR #8</t>
         </is>
@@ -406,50 +630,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Input validations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Input validations</t>
+          <t>Add request and business validations</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Add request and business validations</t>
+          <t>KVS Ganesh</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KVS Ganesh</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
         <is>
           <t>Commit cbd67d0, PR #10</t>
         </is>
@@ -463,50 +667,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Client UI and API hooks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Client UI and API hooks</t>
+          <t>Create UI pages and integrate API calls</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Create UI pages and integrate API calls</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
         <is>
           <t>Commits b6a901d, 75938c0</t>
         </is>
@@ -520,50 +704,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>OTP verification</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OTP verification</t>
+          <t>Set up email OTP verification flow</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Set up email OTP verification flow</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
         <is>
           <t>Commit 4ea730a</t>
         </is>
@@ -577,50 +741,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Automation</t>
+          <t>CI/CD pipeline</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CI/CD pipeline</t>
+          <t>Configure GitHub Actions and DB test service</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Configure GitHub Actions and DB test service</t>
+          <t>Chakrika Sai</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
         <is>
           <t>Commits a0b2625, 2e99047</t>
         </is>
@@ -634,50 +778,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Dashboard and spend tracking</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dashboard and spend tracking</t>
+          <t>Add account dashboard and spending limit view</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Add account dashboard and spending limit view</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
         <is>
           <t>Commit 62150b9, PR #17</t>
         </is>
@@ -691,50 +815,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Status and balance updates</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Status and balance updates</t>
+          <t>Add controllers for status change and balance updates</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Add controllers for status change and balance updates</t>
+          <t>KVS Ganesh</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KVS Ganesh</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Needs Review</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
         <is>
           <t>PR #14, PR #16</t>
         </is>
@@ -748,50 +852,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Lifecycle and integration fixes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lifecycle and integration fixes</t>
+          <t>Finalize payment lifecycle and frontend integration</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Finalize payment lifecycle and frontend integration</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
         <is>
           <t>Commits 060e2d7, cbf0cad</t>
         </is>
@@ -805,61 +889,196 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Sprint updates and tracker maintenance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sprint updates</t>
+          <t>Maintain development updates and task tracker documents</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Maintain development update notes</t>
+          <t>Chakrika Sai</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Commit 2ecbd92</t>
+          <t>Commit 2ecbd92, 2fe3be0, d976421, PR #23</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ST-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CD setup iteration</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Implement and refine CD setup flow</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Commits c4b2b8f, 84139cc, PR #24, PR #25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ST-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pipeline hardening</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Stabilize Jenkins/CD pipeline with test runs and fixes</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Hamsa Suresh</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Commits 39ca9d4, 504cc25, 3f0ac4e, 6ecddd9, PR #26, PR #27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ST-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Client release merge</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Integrate client branch and align repository docs</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>KVS Ganesh</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Commit f7a8745, PR #28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ST-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Client and CI fixes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Merge client updates and fix Jenkins/UI issues</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Commits b4e09c7, ba9a85c, PR #29</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I87"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -911,32 +1130,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Commit</t>
+          <t>PR Merge</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cbf0cad</t>
+          <t>fdc9cdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>Chakrika Sai</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>fix: frontend integration with corrected lifecycle</t>
+          <t>Merge pull request #29 from Neueda-Learning/feat/client</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Integration and Payment Lifecycle</t>
+          <t>Dashboard and Client UI</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -944,21 +1163,19 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="H2" t="n">
+        <v>29</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Delivered in repository history</t>
+          <t>Merged branch: Neueda-Learning/feat/client</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -968,7 +1185,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>060e2d7</t>
+          <t>ba9a85c</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -978,22 +1195,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>fix: payment lifecycle fix</t>
+          <t>fix for jenkin</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Integration and Payment Lifecycle</t>
+          <t>CI/CD Pipeline</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1005,7 +1217,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1015,7 +1227,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4ea730a</t>
+          <t>b4e09c7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1025,22 +1237,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OTP setup and integration done</t>
+          <t>fix: UI enhacements</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OTP Verification</t>
+          <t>Dashboard and Client UI</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1052,7 +1259,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1062,7 +1269,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>370b7ce</t>
+          <t>ec0a8f3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1072,12 +1279,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Merge pull request #15 from Neueda-Learning/feature/ci-setup</t>
+          <t>Merge pull request #28 from Neueda-Learning/feat/client</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CI/CD Pipeline</t>
+          <t>Dashboard and Client UI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1085,19 +1292,19 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H5">
-        <v>15</v>
+      <c r="H5" t="n">
+        <v>28</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feature/ci-setup</t>
+          <t>Merged branch: Neueda-Learning/feat/client</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1107,32 +1314,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7a2e352</t>
+          <t>f7a8745</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>KVS Ganesh</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Merge branch 'main' into feature/ci-setup</t>
+          <t>added a root readme file</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CI/CD Pipeline</t>
+          <t>Documentation and Tracking</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1144,7 +1346,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1154,17 +1356,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2e99047</t>
+          <t>6ecddd9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>Hamsa Suresh</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Configure CI with MySQL service instead of H2</t>
+          <t>fix: jenkin pipeline</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1175,11 +1377,6 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1191,7 +1388,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1201,7 +1398,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>64df6a2</t>
+          <t>024b4f4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1211,12 +1408,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Merge pull request #17 from Neueda-Learning/feat/dashboard</t>
+          <t>Merge pull request #27 from Neueda-Learning/feat/cd</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dashboard and Spending Insights</t>
+          <t>General Engineering</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1224,19 +1421,19 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H8">
-        <v>17</v>
+      <c r="H8" t="n">
+        <v>27</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feat/dashboard</t>
+          <t>Merged branch: Neueda-Learning/feat/cd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1246,32 +1443,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>335ddff</t>
+          <t>3f0ac4e</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>Hamsa Suresh</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Merge branch 'main' of https://github.com/Neueda-Learning/BugHunters_Payment_Processing into feat/dashboard</t>
+          <t>fix: jenkin pipeline fixs</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dashboard and Spending Insights</t>
+          <t>CI/CD Pipeline</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,7 +1475,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1291,8 +1483,10 @@
           <t>PR Merge</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1113580</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6381671</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1301,12 +1495,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Merge pull request #16 from Neueda-Learning/feat/change_status</t>
+          <t>Merge pull request #26 from Neueda-Learning/cd-test</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Status and Balance Updates</t>
+          <t>General Engineering</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1314,19 +1508,19 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H10">
-        <v>16</v>
+      <c r="H10" t="n">
+        <v>26</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feat/change_status</t>
+          <t>Merged branch: Neueda-Learning/cd-test</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1336,7 +1530,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fee286c</t>
+          <t>504cc25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1346,22 +1540,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>controller to change status of the payment</t>
+          <t>Trigger CI/CD test</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Payment and Account APIs</t>
+          <t>CI/CD Pipeline</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1373,32 +1562,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Commit</t>
+          <t>PR Merge</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>c85bf52</t>
+          <t>943edac</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fix backend CI database test configuration</t>
+          <t>Merge pull request #25 from Neueda-Learning/feat/cd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CI/CD Pipeline</t>
+          <t>General Engineering</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1406,21 +1595,19 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="H12" t="n">
+        <v>25</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Delivered in repository history</t>
+          <t>Merged branch: Neueda-Learning/feat/cd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1430,17 +1617,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bfd5106</t>
+          <t>84139cc</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Merge branch 'main' into feature/ci-setup</t>
+          <t>fix: cd setup fix</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1451,11 +1638,6 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1467,32 +1649,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Commit</t>
+          <t>PR Merge</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>a0b2625</t>
+          <t>47af7d5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Added GitHub Actions CI pipeline</t>
+          <t>Merge pull request #24 from Neueda-Learning/feat/cd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CI/CD Pipeline</t>
+          <t>General Engineering</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1500,31 +1682,29 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="H14" t="n">
+        <v>24</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Delivered in repository history</t>
+          <t>Merged branch: Neueda-Learning/feat/cd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PR Merge</t>
+          <t>Commit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>49d7379</t>
+          <t>c4b2b8f</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1534,12 +1714,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Merge pull request #14 from Neueda-Learning/feat/upd_bal</t>
+          <t>cd setup</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>General Engineering</t>
+          <t>CI/CD Pipeline</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1547,19 +1727,16 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H15">
-        <v>14</v>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feat/upd_bal</t>
+          <t>Delivered in repository history</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1569,7 +1746,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>62150b9</t>
+          <t>151242a</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1579,22 +1756,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Added the dashboard to track spending limit</t>
+          <t>Merge branch 'main' of https://github.com/Neueda-Learning/BugHunters_Payment_Processing into feat/cd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dashboard and Spending Insights</t>
+          <t>Payment and Account APIs</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1606,32 +1778,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Commit</t>
+          <t>PR Merge</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5a03db3</t>
+          <t>4f81a37</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KVS Ganesh</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Merge branch 'main' of https://github.com/Neueda-Learning/114_BugHunters into feat/upd_bal</t>
+          <t>Merge pull request #23 from Neueda-Learning/feature/add-docs</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>General Engineering</t>
+          <t>Documentation and Tracking</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1639,21 +1811,19 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="H17" t="n">
+        <v>23</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Delivered in repository history</t>
+          <t>Merged branch: Neueda-Learning/feature/add-docs</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1663,32 +1833,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>d199ed4</t>
+          <t>2fe3be0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KVS Ganesh</t>
+          <t>Chakrika Sai</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>added some controllers</t>
+          <t>Added Task tracker.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Payment and Account APIs</t>
+          <t>Documentation and Tracking</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1700,32 +1865,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PR Merge</t>
+          <t>Commit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>e2f65f3</t>
+          <t>e0393af</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Merge pull request #13 from Neueda-Learning/fix</t>
+          <t>Merge branch 'main' of https://github.com/Neueda-Learning/BugHunters_Payment_Processing into feat/email</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>General Engineering</t>
+          <t>OTP Verification</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1733,44 +1898,41 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H19">
-        <v>13</v>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/fix</t>
+          <t>Delivered in repository history</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Commit</t>
+          <t>PR Merge</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>e038361</t>
+          <t>017e487</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>Chakrika Sai</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Merge branch 'main' of https://github.com/Neueda-Learning/BugHunters_Payment_Processing into fix</t>
+          <t>Merge pull request #22 from Neueda-Learning/feat/dashboard</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>General Engineering</t>
+          <t>Dashboard and Client UI</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1778,21 +1940,19 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="H20" t="n">
+        <v>22</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Delivered in repository history</t>
+          <t>Merged branch: Neueda-Learning/feat/dashboard</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1802,32 +1962,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>287a48e</t>
+          <t>1a153dc</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Merge branch 'main' of https://github.com/Neueda-Learning/BugHunters_Payment_Processing</t>
+          <t>refactor: UI enhacement</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>General Engineering</t>
+          <t>Dashboard and Client UI</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1839,17 +1994,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Commit</t>
+          <t>PR Merge</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2ecbd92</t>
+          <t>d6ffb93</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1859,12 +2014,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Added project development updates documentation</t>
+          <t>Merge pull request #19 from Neueda-Learning/feat/email</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>OTP Verification</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1872,46 +2027,44 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="H22" t="n">
+        <v>19</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Delivered in repository history</t>
+          <t>Merged branch: Neueda-Learning/feat/email</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Commit</t>
+          <t>PR Merge</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>abb61b6</t>
+          <t>e67c884</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>KVS Ganesh</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>integration fix</t>
+          <t>Merge pull request #21 from Neueda-Learning/setup-cd-pipeline</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Integration and Payment Lifecycle</t>
+          <t>CI/CD Pipeline</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1919,46 +2072,44 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="H23" t="n">
+        <v>21</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Delivered in repository history</t>
+          <t>Merged branch: Neueda-Learning/setup-cd-pipeline</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PR Merge</t>
+          <t>Commit</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3f940b9</t>
+          <t>e0a4c41</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>Hamsa Suresh</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Merge pull request #11 from Neueda-Learning/fix</t>
+          <t>modified  cd setup</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>General Engineering</t>
+          <t>CI/CD Pipeline</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1966,19 +2117,16 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H24">
-        <v>11</v>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/fix</t>
+          <t>Delivered in repository history</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1988,7 +2136,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>fe3b8f4</t>
+          <t>0240cab</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1998,22 +2146,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Merge branch 'main' of https://github.com/Neueda-Learning/BugHunters_Payment_Processing into fix</t>
+          <t>Merge branch 'main' of https://github.com/Neueda-Learning/BugHunters_Payment_Processing into feat/email</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>General Engineering</t>
+          <t>OTP Verification</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2025,17 +2168,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PR Merge</t>
+          <t>Commit</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0c67109</t>
+          <t>d976421</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2045,12 +2188,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Merge pull request #10 from Neueda-Learning/feat/valid</t>
+          <t>Update date in development updates document</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>General Engineering</t>
+          <t>Documentation and Tracking</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2058,29 +2201,26 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H26">
-        <v>10</v>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feat/valid</t>
+          <t>Delivered in repository history</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Commit</t>
+          <t>PR Merge</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>cbd67d0</t>
+          <t>2a1c14d</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2090,12 +2230,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Adding the validations part</t>
+          <t>Merge pull request #20 from Neueda-Learning/feature/cd-setup</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>General Engineering</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2103,21 +2243,19 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="H27" t="n">
+        <v>20</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Delivered in repository history</t>
+          <t>Merged branch: Neueda-Learning/feature/cd-setup</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2127,32 +2265,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1ae4243</t>
+          <t>39ca9d4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>Hamsa Suresh</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Merge branch 'main' of https://github.com/Neueda-Learning/BugHunters_Payment_Processing into fix</t>
+          <t>Created cd setup</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>General Engineering</t>
+          <t>CI/CD Pipeline</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2164,16 +2297,18 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PR Merge</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>5433137</v>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>f81ba92</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2182,12 +2317,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Merge pull request #9 from Neueda-Learning/feat/test</t>
+          <t>refactor: dashboard enhacement</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Dashboard and Client UI</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2195,19 +2330,16 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H29">
-        <v>9</v>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feat/test</t>
+          <t>Delivered in repository history</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2215,8 +2347,10 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="C30">
-        <v>6370222</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>f0999f8</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2225,22 +2359,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>fix: key generated on server side</t>
+          <t>Align the test case according to correct lifecycle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>General Engineering</t>
+          <t>Integration and Payment Lifecycle</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2252,17 +2381,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PR Merge</t>
+          <t>Commit</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3354d99</t>
+          <t>cbf0cad</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2272,12 +2401,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Merge pull request #8 from Neueda-Learning/feat/exception</t>
+          <t>fix: frontend integration with corrected lifecycle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Exception Handling</t>
+          <t>Integration and Payment Lifecycle</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2285,19 +2414,16 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H31">
-        <v>8</v>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feat/exception</t>
+          <t>Delivered in repository history</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2307,7 +2433,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>581f819</t>
+          <t>060e2d7</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2317,22 +2443,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>fix: correcting the error code as per the description</t>
+          <t>fix: payment lifecycle fix</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>General Engineering</t>
+          <t>Integration and Payment Lifecycle</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2344,17 +2465,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PR Merge</t>
+          <t>Commit</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>612f5e8</t>
+          <t>4ea730a</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2364,12 +2485,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Merge pull request #6 from Neueda-Learning/feature/exception</t>
+          <t>OTP setup and integration done</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Exception Handling</t>
+          <t>OTP Verification</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2377,19 +2498,16 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H33">
-        <v>6</v>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feature/exception</t>
+          <t>Delivered in repository history</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2399,22 +2517,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>6ede01b</t>
+          <t>370b7ce</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>Hamsa Suresh</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Merge pull request #7 from Neueda-Learning/feat/client</t>
+          <t>Merge pull request #15 from Neueda-Learning/feature/ci-setup</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>General Engineering</t>
+          <t>CI/CD Pipeline</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2422,19 +2540,19 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H34">
-        <v>7</v>
+      <c r="H34" t="n">
+        <v>15</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feat/client</t>
+          <t>Merged branch: Neueda-Learning/feature/ci-setup</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2444,32 +2562,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>75938c0</t>
+          <t>7a2e352</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>Chakrika Sai</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>defining function to call apis</t>
+          <t>Merge branch 'main' into feature/ci-setup</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Payment and Account APIs</t>
+          <t>CI/CD Pipeline</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2481,7 +2594,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2491,32 +2604,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>b6a901d</t>
+          <t>2e99047</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>Chakrika Sai</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Basic UI pages</t>
+          <t>Configure CI with MySQL service instead of H2</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>General Engineering</t>
+          <t>CI/CD Pipeline</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2528,17 +2636,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Commit</t>
+          <t>PR Merge</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0bbdc5e</t>
+          <t>64df6a2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2548,12 +2656,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>added unit testing part</t>
+          <t>Merge pull request #17 from Neueda-Learning/feat/dashboard</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Dashboard and Spending Insights</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2561,21 +2669,19 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="H37" t="n">
+        <v>17</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Delivered in repository history</t>
+          <t>Merged branch: Neueda-Learning/feat/dashboard</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2585,32 +2691,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>05ab7e0</t>
+          <t>335ddff</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KVS Ganesh</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Added Validations</t>
+          <t>Merge branch 'main' of https://github.com/Neueda-Learning/BugHunters_Payment_Processing into feat/dashboard</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Dashboard and Spending Insights</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2622,32 +2723,30 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Commit</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>8820d8a</t>
-        </is>
+          <t>PR Merge</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1113580</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>KVS Ganesh</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Exception folder created</t>
+          <t>Merge pull request #16 from Neueda-Learning/feat/change_status</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Exception Handling</t>
+          <t>Status and Balance Updates</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2655,21 +2754,19 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="H39" t="n">
+        <v>16</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Delivered in repository history</t>
+          <t>Merged branch: Neueda-Learning/feat/change_status</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2679,32 +2776,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ab7d051</t>
+          <t>fee286c</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KVS Ganesh</t>
+          <t>Hamsa Suresh</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Added JPA extension for Account table</t>
+          <t>controller to change status of the payment</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Account Schema and JPA</t>
+          <t>Payment and Account APIs</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2716,7 +2808,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2726,32 +2818,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1c57902</t>
+          <t>c85bf52</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KVS Ganesh</t>
+          <t>Chakrika Sai</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Added Account table</t>
+          <t>Fix backend CI database test configuration</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Account Schema and JPA</t>
+          <t>CI/CD Pipeline</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2763,17 +2850,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PR Merge</t>
+          <t>Commit</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>520a481</t>
+          <t>bfd5106</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2783,42 +2870,39 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>WIP on main: 07ac5a8 Merge pull request #3 from Neueda-Learning/feat/schema</t>
+          <t>Merge branch 'main' into feature/ci-setup</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Account Schema and JPA</t>
+          <t>CI/CD Pipeline</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="H42">
-        <v>3</v>
+          <t>Completed</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Work in progress marker</t>
+          <t>Delivered in repository history</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PR Merge</t>
+          <t>Commit</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2badb0a</t>
+          <t>a0b2625</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2828,12 +2912,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>index on main: 07ac5a8 Merge pull request #3 from Neueda-Learning/feat/schema</t>
+          <t>Added GitHub Actions CI pipeline</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Account Schema and JPA</t>
+          <t>CI/CD Pipeline</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2841,19 +2925,16 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H43">
-        <v>3</v>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feat/schema</t>
+          <t>Delivered in repository history</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2863,22 +2944,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0ec65bd</t>
+          <t>49d7379</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>untracked files on main: 07ac5a8 Merge pull request #3 from Neueda-Learning/feat/schema</t>
+          <t>Merge pull request #14 from Neueda-Learning/feat/upd_bal</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Account Schema and JPA</t>
+          <t>General Engineering</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2886,19 +2967,19 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H44">
-        <v>3</v>
+      <c r="H44" t="n">
+        <v>14</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feat/schema</t>
+          <t>Merged branch: Neueda-Learning/feat/upd_bal</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2908,32 +2989,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ffcfbb3</t>
+          <t>62150b9</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KVS Ganesh</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>newly added the account table</t>
+          <t>Added the dashboard to track spending limit</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Account Schema and JPA</t>
+          <t>Dashboard and Spending Insights</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2945,7 +3021,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2955,7 +3031,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>e774acc</t>
+          <t>5a03db3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2965,22 +3041,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>newly added the account table</t>
+          <t>Merge branch 'main' of https://github.com/Neueda-Learning/114_BugHunters into feat/upd_bal</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Account Schema and JPA</t>
+          <t>General Engineering</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2992,25 +3063,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PR Merge</t>
-        </is>
-      </c>
-      <c r="C47">
-        <v>7788615</v>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>d199ed4</t>
+        </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>KVS Ganesh</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Merge pull request #5 from Neueda-Learning/feat/endpoints</t>
+          <t>added some controllers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3023,44 +3096,41 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H47">
-        <v>5</v>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feat/endpoints</t>
+          <t>Delivered in repository history</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Commit</t>
+          <t>PR Merge</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>39fa8de</t>
+          <t>e2f65f3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Hamsa Suresh</t>
+          <t>Chakrika Sai</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Created some more endpoints</t>
+          <t>Merge pull request #13 from Neueda-Learning/fix</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Payment and Account APIs</t>
+          <t>General Engineering</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3068,46 +3138,44 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="H48" t="n">
+        <v>13</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Delivered in repository history</t>
+          <t>Merged branch: Neueda-Learning/fix</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PR Merge</t>
+          <t>Commit</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>e53f235</t>
+          <t>e038361</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Merge pull request #4 from Neueda-Learning/feat/endpoints</t>
+          <t>Merge branch 'main' of https://github.com/Neueda-Learning/BugHunters_Payment_Processing into fix</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Payment and Account APIs</t>
+          <t>General Engineering</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3115,19 +3183,16 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H49">
-        <v>4</v>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feat/endpoints</t>
+          <t>Delivered in repository history</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3137,32 +3202,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>73685f9</t>
+          <t>287a48e</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>Chakrika Sai</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Created endpoint to create and get payment details</t>
+          <t>Merge branch 'main' of https://github.com/Neueda-Learning/BugHunters_Payment_Processing</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Payment and Account APIs</t>
+          <t>General Engineering</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3174,32 +3234,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PR Merge</t>
+          <t>Commit</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>07ac5a8</t>
+          <t>2ecbd92</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>Chakrika Sai</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Merge pull request #3 from Neueda-Learning/feat/schema</t>
+          <t>Added project development updates documentation</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Account Schema and JPA</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3207,19 +3267,16 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H51">
-        <v>3</v>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feat/schema</t>
+          <t>Delivered in repository history</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3229,32 +3286,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>df81852</t>
+          <t>abb61b6</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>KVS Ganesh</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>created table in db and schema attached for reference</t>
+          <t>integration fix</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Account Schema and JPA</t>
+          <t>Integration and Payment Lifecycle</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3266,7 +3318,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3276,7 +3328,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0f0d8b7</t>
+          <t>3f940b9</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3286,7 +3338,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Merge pull request #2 from Neueda-Learning/feature/payment-models</t>
+          <t>Merge pull request #11 from Neueda-Learning/fix</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3299,19 +3351,19 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H53">
-        <v>2</v>
+      <c r="H53" t="n">
+        <v>11</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feature/payment-models</t>
+          <t>Merged branch: Neueda-Learning/fix</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3321,7 +3373,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>7e4e521</t>
+          <t>fe3b8f4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3331,22 +3383,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Changed datatype of status from String to enum</t>
+          <t>Merge branch 'main' of https://github.com/Neueda-Learning/BugHunters_Payment_Processing into fix</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Payment Models</t>
+          <t>General Engineering</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3358,32 +3405,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Commit</t>
+          <t>PR Merge</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>8a2f299</t>
+          <t>0c67109</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>Chakrika Sai</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Added JPA annotation to the tables</t>
+          <t>Merge pull request #10 from Neueda-Learning/feat/valid</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Account Schema and JPA</t>
+          <t>General Engineering</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3391,46 +3438,44 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="H55" t="n">
+        <v>10</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Delivered in repository history</t>
+          <t>Merged branch: Neueda-Learning/feat/valid</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PR Merge</t>
+          <t>Commit</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0c4c766</t>
+          <t>cbd67d0</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
+          <t>KVS Ganesh</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Merge pull request #1 from Neueda-Learning/feature/payment-models</t>
+          <t>Adding the validations part</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>General Engineering</t>
+          <t>Input Validation</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3438,19 +3483,16 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H56">
-        <v>1</v>
-      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Merged branch: Neueda-Learning/feature/payment-models</t>
+          <t>Delivered in repository history</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3460,32 +3502,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ef6ea7f</t>
+          <t>1ae4243</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
+          <t>Rachit Goyal</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Added Payment and PaymentHistory models</t>
+          <t>Merge branch 'main' of https://github.com/Neueda-Learning/BugHunters_Payment_Processing into fix</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Payment Models</t>
+          <t>General Engineering</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>Completed</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3497,56 +3534,1306 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PR Merge</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>5433137</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Merge pull request #9 from Neueda-Learning/feat/test</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>9</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Merged branch: Neueda-Learning/feat/test</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>6370222</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>fix: key generated on server side</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>General Engineering</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PR Merge</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3354d99</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Merge pull request #8 from Neueda-Learning/feat/exception</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Exception Handling</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>8</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Merged branch: Neueda-Learning/feat/exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>581f819</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>fix: correcting the error code as per the description</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>General Engineering</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PR Merge</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>612f5e8</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Merge pull request #6 from Neueda-Learning/feature/exception</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Exception Handling</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>6</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Merged branch: Neueda-Learning/feature/exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PR Merge</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>6ede01b</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Merge pull request #7 from Neueda-Learning/feat/client</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>General Engineering</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>7</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Merged branch: Neueda-Learning/feat/client</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>75938c0</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>defining function to call apis</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Payment and Account APIs</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>b6a901d</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Basic UI pages</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>General Engineering</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0bbdc5e</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Hamsa Suresh</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>added unit testing part</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>05ab7e0</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>KVS Ganesh</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Added Validations</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>8820d8a</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Chakrika Sai</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Exception folder created</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Exception Handling</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ab7d051</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>KVS Ganesh</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Added JPA extension for Account table</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Account Schema and JPA</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1c57902</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>KVS Ganesh</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Added Account table</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Account Schema and JPA</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PR Merge</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>520a481</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Chakrika Sai</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>WIP on main: 07ac5a8 Merge pull request #3 from Neueda-Learning/feat/schema</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Account Schema and JPA</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>3</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Work in progress marker</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PR Merge</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2badb0a</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Chakrika Sai</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>index on main: 07ac5a8 Merge pull request #3 from Neueda-Learning/feat/schema</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Account Schema and JPA</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>3</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Merged branch: Neueda-Learning/feat/schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PR Merge</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>0ec65bd</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Chakrika Sai</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>untracked files on main: 07ac5a8 Merge pull request #3 from Neueda-Learning/feat/schema</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Account Schema and JPA</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>3</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Merged branch: Neueda-Learning/feat/schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ffcfbb3</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>KVS Ganesh</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>newly added the account table</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Account Schema and JPA</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>e774acc</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>KVS Ganesh</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>newly added the account table</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Account Schema and JPA</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PR Merge</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>7788615</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Merge pull request #5 from Neueda-Learning/feat/endpoints</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Payment and Account APIs</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>5</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Merged branch: Neueda-Learning/feat/endpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>39fa8de</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Hamsa Suresh</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Created some more endpoints</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Payment and Account APIs</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PR Merge</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>e53f235</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Chakrika Sai</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Merge pull request #4 from Neueda-Learning/feat/endpoints</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Payment and Account APIs</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>4</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Merged branch: Neueda-Learning/feat/endpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>73685f9</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Created endpoint to create and get payment details</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Payment and Account APIs</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PR Merge</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>07ac5a8</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Merge pull request #3 from Neueda-Learning/feat/schema</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Account Schema and JPA</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>3</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Merged branch: Neueda-Learning/feat/schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>df81852</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>KVS Ganesh</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>created table in db and schema attached for reference</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Account Schema and JPA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PR Merge</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0f0d8b7</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Chakrika Sai</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Merge pull request #2 from Neueda-Learning/feature/payment-models</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>General Engineering</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>2</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Merged branch: Neueda-Learning/feature/payment-models</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Commit</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>7e4e521</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Changed datatype of status from String to enum</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Payment Models</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>8a2f299</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Added JPA annotation to the tables</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Account Schema and JPA</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PR Merge</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0c4c766</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Merge pull request #1 from Neueda-Learning/feature/payment-models</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>General Engineering</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Merged branch: Neueda-Learning/feature/payment-models</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ef6ea7f</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Chakrika Sai</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Added Payment and PaymentHistory models</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Payment Models</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Delivered in repository history</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
         <is>
           <t>06d75ea</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Rachit Goyal</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Initial commit</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>General Engineering</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
         <is>
           <t>Delivered in repository history</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3571,8 +4858,8 @@
           <t>Total Stories</t>
         </is>
       </c>
-      <c r="B2">
-        <v>13</v>
+      <c r="B2" t="n">
+        <v>17</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3586,8 +4873,8 @@
           <t>Completed Stories</t>
         </is>
       </c>
-      <c r="B3">
-        <v>13</v>
+      <c r="B3" t="n">
+        <v>17</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3601,7 +4888,7 @@
           <t>In Progress Stories</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -3616,8 +4903,8 @@
           <t>Stories Needing Review</t>
         </is>
       </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="B5" t="n">
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3631,8 +4918,8 @@
           <t>PR Merges Logged</t>
         </is>
       </c>
-      <c r="B6">
-        <v>19</v>
+      <c r="B6" t="n">
+        <v>30</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3646,8 +4933,8 @@
           <t>Total History Entries</t>
         </is>
       </c>
-      <c r="B7">
-        <v>57</v>
+      <c r="B7" t="n">
+        <v>86</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3663,29 +4950,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>Tracker generated automatically</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
     </row>
@@ -3709,30 +4979,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rachit Goyal</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>25</v>
+          <t>Chakrika Sai</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>22</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PR merges: 8</t>
+          <t>PR merges: 11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chakrika Sai</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>17</v>
+          <t>Hamsa Suresh</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>12</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PR merges: 8</t>
+          <t>PR merges: 4</t>
         </is>
       </c>
     </row>
@@ -3742,30 +5012,31 @@
           <t>KVS Ganesh</t>
         </is>
       </c>
-      <c r="B13">
-        <v>10</v>
+      <c r="B13" t="n">
+        <v>14</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PR merges: 1</t>
+          <t>PR merges: 4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hamsa Suresh</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>5</v>
+          <t>Rachit Goyal</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>38</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PR merges: 2</t>
+          <t>PR merges: 11</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>